--- a/examples/sample_cost.xlsx
+++ b/examples/sample_cost.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>素水泥浆</t>
+          <t>C20预拌砂浆</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>520</v>
+        <v>455</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -492,7 +492,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>DS20预拌水泥砂浆</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>485</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -513,23 +513,161 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>素水泥浆</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>520</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>稀水泥浆</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>530</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>花岗岩石板</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20mm</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>320</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>盲道花岗岩石砖</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>300*300*25</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>480</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>警示带花岗岩石材</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>300*130</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>350</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>综合工日</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>装饰工程</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>工日</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D11" t="n">
         <v>135</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>人工</t>
         </is>
